--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="358">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,13 +105,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>CommunicationRequest</t>
+    <t>Consent</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/CommunicationRequest</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Consent</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -240,10 +237,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: HL7 v2 Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t/>
@@ -259,19 +259,25 @@
 </t>
   </si>
   <si>
-    <t>A request for information to be sent to a receiver</t>
-  </si>
-  <si>
-    <t>A request to convey information; e.g. the CDS system proposes that an alert be sent to a responsible provider, the CDS system proposes that the public health agency be notified about a reportable condition.</t>
-  </si>
-  <si>
-    <t>Request</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.id</t>
+    <t>A healthcare consumer's  choices to permit or deny recipients or roles to perform actions for specific purposes and periods of time</t>
+  </si>
+  <si>
+    <t>A record of a healthcare consumer’s  choices, which permits or denies identified recipient(s) or recipient role(s) to perform one or more actions within a given policy context, for specific purposes and periods of time.</t>
+  </si>
+  <si>
+    <t>Broadly, there are 3 key areas of consent for patients: Consent around sharing information (aka Privacy Consent Directive - Authorization to Collect, Use, or Disclose information), consent for specific treatment, or kinds of treatment, and general advance care directives.</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>FinancialConsent</t>
+  </si>
+  <si>
+    <t>Consent.id</t>
   </si>
   <si>
     <t>1</t>
@@ -296,7 +302,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>CommunicationRequest.meta</t>
+    <t>Consent.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -316,7 +322,7 @@
 </t>
   </si>
   <si>
-    <t>CommunicationRequest.implicitRules</t>
+    <t>Consent.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -335,7 +341,7 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>CommunicationRequest.language</t>
+    <t>Consent.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -363,7 +369,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>CommunicationRequest.text</t>
+    <t>Consent.text</t>
   </si>
   <si>
     <t>narrative
@@ -389,7 +395,7 @@
     <t>Act.text?</t>
   </si>
   <si>
-    <t>CommunicationRequest.contained</t>
+    <t>Consent.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -415,7 +421,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>CommunicationRequest.extension</t>
+    <t>Consent.extension</t>
   </si>
   <si>
     <t>extensions
@@ -442,7 +448,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>CommunicationRequest.modifierExtension</t>
+    <t>Consent.modifierExtension</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -458,545 +464,675 @@
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>CommunicationRequest.identifier</t>
+    <t>Consent.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Unique identifier</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this communication request by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the communication request as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t>Request.identifier</t>
+    <t>Identifier for this record (external references)</t>
+  </si>
+  <si>
+    <t>Unique identifier for this copy of the Consent Statement.</t>
+  </si>
+  <si>
+    <t>This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
+  </si>
+  <si>
+    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="urn:ietf:rfc:3986"/&gt;
+  &lt;value value="Local eCMS identifier"/&gt;
+&lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>CommunicationRequest.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
+    <t>Consent.status</t>
+  </si>
+  <si>
+    <t>draft | proposed | active | rejected | inactive | entered-in-error</t>
+  </si>
+  <si>
+    <t>Indicates the current state of this consent.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains the codes rejected and entered-in-error that mark the Consent as not currently valid.</t>
+  </si>
+  <si>
+    <t>The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Indicates the state of the consent.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>HL7 Table 0498 - Consent Status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Consent.scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Which of the four areas this resource covers (extensible)</t>
+  </si>
+  <si>
+    <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="patient-privacy"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>The four anticipated uses for the Consent Resource.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+  </si>
+  <si>
+    <t>Consent.category</t>
+  </si>
+  <si>
+    <t>Classification of the consent statement - for indexing/retrieval</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="59284-0"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A classification of the type of consents found in a consent statement.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>HL7 Table 0497 - Consent Type</t>
+  </si>
+  <si>
+    <t>CNTRCT</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Consent.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient)
+</t>
+  </si>
+  <si>
+    <t>Who the consent applies to</t>
+  </si>
+  <si>
+    <t>The patient/healthcare consumer to whom this consent applies.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Consent.dateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>When this Consent was created or indexed</t>
+  </si>
+  <si>
+    <t>When this  Consent was issued / created / indexed.</t>
+  </si>
+  <si>
+    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>Field 13/ Consent Decision Date</t>
+  </si>
+  <si>
+    <t>FinancialConsent effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Consent.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consentor
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Who is agreeing to the policy and rules</t>
+  </si>
+  <si>
+    <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
+  </si>
+  <si>
+    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>Field 24/ ConsenterID</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Consent.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">custodian
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Custodian of the consent</t>
+  </si>
+  <si>
+    <t>The organization that manages the consent, and the framework within which it is executed.</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Consent.source[x]</t>
+  </si>
+  <si>
+    <t>Attachment
+Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+  </si>
+  <si>
+    <t>Source from which this consent is taken</t>
+  </si>
+  <si>
+    <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
+  </si>
+  <si>
+    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+  </si>
+  <si>
+    <t>Field 19 Informational Material Supplied Indicator</t>
+  </si>
+  <si>
+    <t>Consent.policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Policies covered by this consent</t>
+  </si>
+  <si>
+    <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
+  </si>
+  <si>
+    <t>Consent.policy.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.policy.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.policy.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.policy.authority</t>
+  </si>
+  <si>
+    <t>Enforcement source for policy</t>
+  </si>
+  <si>
+    <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ppc-1
+</t>
+  </si>
+  <si>
+    <t>Consent.policy.uri</t>
+  </si>
+  <si>
+    <t>Specific policy covered by this consent</t>
+  </si>
+  <si>
+    <t>This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
+  </si>
+  <si>
+    <t>Consent.policyRule</t>
+  </si>
+  <si>
+    <t>Regulation that this consents to</t>
+  </si>
+  <si>
+    <t>A reference to the specific base computable regulation or policy.</t>
+  </si>
+  <si>
+    <t>If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
+  </si>
+  <si>
+    <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
+  </si>
+  <si>
+    <t>Regulatory policy examples.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+  </si>
+  <si>
+    <t>Consent.verification</t>
+  </si>
+  <si>
+    <t>Consent Verified by patient or family</t>
+  </si>
+  <si>
+    <t>Whether a treatment instruction (e.g. artificial respiration yes or no) was verified with the patient, his/her family or another authorized person.</t>
+  </si>
+  <si>
+    <t>Consent.verification.id</t>
+  </si>
+  <si>
+    <t>Consent.verification.extension</t>
+  </si>
+  <si>
+    <t>Consent.verification.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.verification.verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Has been verified</t>
+  </si>
+  <si>
+    <t>Has the instruction been verified.</t>
+  </si>
+  <si>
+    <t>Consent.verification.verifiedWith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Person who verified</t>
+  </si>
+  <si>
+    <t>Who verified the instruction (Patient, Relative or other Authorized Person).</t>
+  </si>
+  <si>
+    <t>Consent.verification.verificationDate</t>
+  </si>
+  <si>
+    <t>When consent verified</t>
+  </si>
+  <si>
+    <t>Date verification was collected.</t>
+  </si>
+  <si>
+    <t>Consent.provision</t>
+  </si>
+  <si>
+    <t>Constraints to the base Consent.policyRule</t>
+  </si>
+  <si>
+    <t>An exception to the base policy of this consent. An exception can be an addition or removal of access permissions.</t>
+  </si>
+  <si>
+    <t>Consent.provision.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.type</t>
+  </si>
+  <si>
+    <t>deny | permit</t>
+  </si>
+  <si>
+    <t>Action  to take - permit or deny - when the rule conditions are met.  Not permitted in root rule, required in all nested rules.</t>
+  </si>
+  <si>
+    <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Consent.provision.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Timeframe for this rule</t>
+  </si>
+  <si>
+    <t>The timeframe in this rule is valid.</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor</t>
+  </si>
+  <si>
+    <t>Who|what controlled by this rule (or group, by role)</t>
+  </si>
+  <si>
+    <t>Who or what is controlled by this rule. Use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+  </si>
+  <si>
+    <t>There is no specific actor associated with the exception</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor.role</t>
+  </si>
+  <si>
+    <t>How the actor is involved</t>
+  </si>
+  <si>
+    <t>How the individual is involved in the resources content that is described in the exception.</t>
+  </si>
+  <si>
+    <t>How an actor is involved in the consent considerations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+  </si>
+  <si>
+    <t>Consent.provision.actor.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>Resource for the actor (or group, by role)</t>
+  </si>
+  <si>
+    <t>The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+  </si>
+  <si>
+    <t>Consent.provision.action</t>
+  </si>
+  <si>
+    <t>Actions controlled by this rule</t>
+  </si>
+  <si>
+    <t>Actions controlled by this Rule.</t>
+  </si>
+  <si>
+    <t>Note that this is the direct action (not the grounds for the action covered in the purpose element). At present, the only action in the understood and tested scope of this resource is 'read'.</t>
+  </si>
+  <si>
+    <t>all actions</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Detailed codes for the consent action.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+  </si>
+  <si>
+    <t>Consent.provision.securityLabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels that define affected resources</t>
+  </si>
+  <si>
+    <t>A security label, comprised of 0..* security label fields (Privacy tags), which define which resources are controlled by this exception.</t>
+  </si>
+  <si>
+    <t>If the consent specifies a security label of "R" then it applies to all resources that are labeled "R" or lower. E.g. for Confidentiality, it's a high water mark. For other kinds of security labels, subsumption logic applies. When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Consent.provision.purpose</t>
+  </si>
+  <si>
+    <t>Context of activities covered by this rule</t>
+  </si>
+  <si>
+    <t>The context of the activities a user is taking - why the user is accessing the data - that are controlled by this rule.</t>
+  </si>
+  <si>
+    <t>When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
+  </si>
+  <si>
+    <t>What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
+  </si>
+  <si>
+    <t>Consent.provision.class</t>
+  </si>
+  <si>
+    <t>e.g. Resource Type, Profile, CDA, etc.</t>
+  </si>
+  <si>
+    <t>The class of information covered by this rule. The type can be a FHIR resource type, a profile on a type, or a CDA document, or some other type that indicates what sort of information the consent relates to.</t>
+  </si>
+  <si>
+    <t>Multiple types are or'ed together. The intention of the contentType element is that the codes refer to profiles or document types defined in a standard or an implementation guide somewhere.</t>
+  </si>
+  <si>
+    <t>The class (type) of information a consent rule covers.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+  </si>
+  <si>
+    <t>Consent.provision.code</t>
+  </si>
+  <si>
+    <t>e.g. LOINC or SNOMED CT code, etc. in the content</t>
+  </si>
+  <si>
+    <t>If this code is found in an instance, then the rule applies.</t>
+  </si>
+  <si>
+    <t>Typical use of this is a Document code with class = CDA.</t>
+  </si>
+  <si>
+    <t>If this code is found in an instance, then the exception applies.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+  </si>
+  <si>
+    <t>Consent.provision.dataPeriod</t>
+  </si>
+  <si>
+    <t>Timeframe for data controlled by this rule</t>
+  </si>
+  <si>
+    <t>Clinical or Operational Relevant period of time that bounds the data controlled by this rule.</t>
+  </si>
+  <si>
+    <t>This has a different sense to the Consent.period - that is when the consent agreement holds. This is the time period of the data that is controlled by the agreement.</t>
+  </si>
+  <si>
+    <t>Consent.provision.data</t>
+  </si>
+  <si>
+    <t>Data controlled by this rule</t>
+  </si>
+  <si>
+    <t>The resources controlled by this rule if specific resources are referenced.</t>
+  </si>
+  <si>
+    <t>all data</t>
+  </si>
+  <si>
+    <t>Consent.provision.data.id</t>
+  </si>
+  <si>
+    <t>Consent.provision.data.extension</t>
+  </si>
+  <si>
+    <t>Consent.provision.data.modifierExtension</t>
+  </si>
+  <si>
+    <t>Consent.provision.data.meaning</t>
+  </si>
+  <si>
+    <t>instance | related | dependents | authoredby</t>
+  </si>
+  <si>
+    <t>How the resource reference is interpreted when testing consent restrictions.</t>
+  </si>
+  <si>
+    <t>How a resource reference is interpreted when testing consent restrictions.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.0.1</t>
+  </si>
+  <si>
+    <t>Consent.provision.data.reference</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
-    <t>Fulfills plan or proposal</t>
-  </si>
-  <si>
-    <t>A plan or proposal that is fulfilled in whole or in part by this request.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the request and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>Request.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.replaces</t>
-  </si>
-  <si>
-    <t>supersedes
-prior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CommunicationRequest)
-</t>
-  </si>
-  <si>
-    <t>Request(s) replaced by this request</t>
-  </si>
-  <si>
-    <t>Completed or terminated request(s) whose function is taken by this new request.</t>
-  </si>
-  <si>
-    <t>The replacement could be because the initial request was immediately rejected (due to an issue) or because the previous request was completed, but the need for the action described by the request remains ongoing.</t>
-  </si>
-  <si>
-    <t>Allows tracing the continuation of a therapy or administrative process instantiated through multiple requests.</t>
-  </si>
-  <si>
-    <t>Request.replaces</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RPLC].target</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.groupIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grouperId
-</t>
-  </si>
-  <si>
-    <t>Composite request this is part of</t>
-  </si>
-  <si>
-    <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition, prescription or similar form.</t>
-  </si>
-  <si>
-    <t>Requests are linked either by a "basedOn" relationship (i.e. one request is fulfilling another) or by having a common requisition.  Requests that are part of the same requisition are generally treated independently from the perspective of changing their state or maintaining them after initial creation.</t>
-  </si>
-  <si>
-    <t>Request.groupIdentifier</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.status</t>
-  </si>
-  <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>The status of the proposal or order.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The status of the communication request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.statusReason</t>
-  </si>
-  <si>
-    <t>Suspended Reason
-Cancelled Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the CommunicationRequest.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled".  The reason why the CommunicationRequest was created at all is captured in reasonCode, not here.  [distinct reason codes for different statuses can be enforced using invariants if they are universal bindings].</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying the reason for the current state of a request.</t>
-  </si>
-  <si>
-    <t>Request.statusReason</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN].reasonCOde</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.category</t>
-  </si>
-  <si>
-    <t>Message category</t>
-  </si>
-  <si>
-    <t>The type of message to be sent such as alert, notification, reminder, instruction, etc.</t>
-  </si>
-  <si>
-    <t>There may be multiple axes of categorization and one communication request may serve multiple purposes.</t>
-  </si>
-  <si>
-    <t>Codes for general categories of communications such as alerts, instruction, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/communication-category</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.priority</t>
-  </si>
-  <si>
-    <t>routine | urgent | asap | stat</t>
-  </si>
-  <si>
-    <t>Characterizes how quickly the proposed act must be initiated. Includes concepts such as stat, urgent, routine.</t>
-  </si>
-  <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>Codes indicating the relative importance of a communication request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.priority</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.doNotPerform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prohibited
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>True if request is prohibiting action</t>
-  </si>
-  <si>
-    <t>If true indicates that the CommunicationRequest is asking for the specified action to *not* occur.</t>
-  </si>
-  <si>
-    <t>The attributes provided with the request qualify what is not to be done.</t>
-  </si>
-  <si>
-    <t>If do not perform is not specified, the request is a positive request e.g. "do perform"</t>
-  </si>
-  <si>
-    <t>Request.doNotPerform</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.medium</t>
-  </si>
-  <si>
-    <t>A channel of communication</t>
-  </si>
-  <si>
-    <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ParticipationMode</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Group)
-</t>
-  </si>
-  <si>
-    <t>Focus of message</t>
-  </si>
-  <si>
-    <t>The patient or group that is the focus of this communication request.</t>
-  </si>
-  <si>
-    <t>Request.subject</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.about</t>
-  </si>
-  <si>
-    <t>Resources that pertain to this communication request</t>
-  </si>
-  <si>
-    <t>Other resources that pertain to this communication request and to which this communication request should be associated.</t>
-  </si>
-  <si>
-    <t>Don't use CommunicationRequest.about element when a more specific element exists, such as basedOn, reasonReference, or replaces.</t>
-  </si>
-  <si>
-    <t>Request.supportingInfo</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter)
-</t>
-  </si>
-  <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this CommunicationRequest was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
-  </si>
-  <si>
-    <t>Request.context</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Message payload</t>
-  </si>
-  <si>
-    <t>Text, attachment(s), or resource(s) to be communicated to the recipient.</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.payload.content[x]</t>
-  </si>
-  <si>
-    <t>string
-AttachmentReference(Resource)</t>
-  </si>
-  <si>
-    <t>Message part content</t>
-  </si>
-  <si>
-    <t>The communicated content (or for multi-part communications, one portion of the communication).</t>
-  </si>
-  <si>
-    <t>Request.note</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.occurrence[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">timing
-</t>
-  </si>
-  <si>
-    <t>dateTime
-Period</t>
-  </si>
-  <si>
-    <t>When scheduled</t>
-  </si>
-  <si>
-    <t>The time when this communication is to occur.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">createdOn
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>When request transitioned to being actionable</t>
-  </si>
-  <si>
-    <t>For draft requests, indicates the date of initial creation.  For requests with other statuses, indicates the date of activation.</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.requester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
-</t>
-  </si>
-  <si>
-    <t>Who/what is requesting service</t>
-  </si>
-  <si>
-    <t>The device, individual, or organization who initiated the request and has responsibility for its activation.</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.recipient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson|Group|CareTeam|HealthcareService)
-</t>
-  </si>
-  <si>
-    <t>Message recipient</t>
-  </si>
-  <si>
-    <t>The entity (e.g. person, organization, clinical information system, device, group, or care team) which is the intended target of the communication.</t>
-  </si>
-  <si>
-    <t>Request.performer</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.sender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson|HealthcareService)
-</t>
-  </si>
-  <si>
-    <t>Message sender</t>
-  </si>
-  <si>
-    <t>The entity (e.g. person, organization, clinical information system, or device) which is to be the source of the communication.</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.reasonCode</t>
-  </si>
-  <si>
-    <t>Why is communication needed?</t>
-  </si>
-  <si>
-    <t>Describes why the request is being made in coded or textual form.</t>
-  </si>
-  <si>
-    <t>Textual reasons can be captured using reasonCode.text.</t>
-  </si>
-  <si>
-    <t>Codes for describing reasons for the occurrence of a communication.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActReason</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
-</t>
-  </si>
-  <si>
-    <t>Indicates another resource whose existence justifies this request.</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>CommunicationRequest.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments made about communication request</t>
-  </si>
-  <si>
-    <t>Comments made about the request by the requester, sender, recipient, subject or other participants.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=ANNGEN, moodCode=EVN].value[xsi:type=ST]</t>
+    <t>The actual data reference</t>
+  </si>
+  <si>
+    <t>A reference to a specific resource that defines which resources are covered by this consent.</t>
+  </si>
+  <si>
+    <t>Consent.provision.provision</t>
+  </si>
+  <si>
+    <t>Nested Exception Rules</t>
+  </si>
+  <si>
+    <t>Rules which provide exceptions to the base rule or subrules.</t>
   </si>
 </sst>
 </file>
@@ -1125,21 +1261,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1313,11 +1434,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.09765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.09765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.04296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1326,7 +1447,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1335,25 +1456,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="42.44921875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="74.45703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.62109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="97.8125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.85546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1474,8 +1596,11 @@
       <c r="AM1" t="s" s="1">
         <v>75</v>
       </c>
+      <c r="AN1" t="s" s="1">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1484,2466 +1609,2528 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="AN2" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN3" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN4" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN5" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN6" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>153</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>165</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>183</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>76</v>
+        <v>190</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>191</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>200</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>76</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>209</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q18" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>215</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q19" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>137</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>76</v>
+      <c r="AN22" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>76</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>241</v>
@@ -3954,410 +4141,422 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>248</v>
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>257</v>
       </c>
@@ -4366,999 +4565,3512 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>263</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>231</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>309</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q40" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Y46" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM36" t="s" s="2">
+      <c r="Z46" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>312</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM36">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI35">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="419">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -544,13 +544,6 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="patient-privacy"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -558,6 +551,223 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+  </si>
+  <si>
+    <t>Consent.scope.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.scope.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/consentscope</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>patient-privacy</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Consent.scope.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -732,29 +942,7 @@
     <t>Consent.policy.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Consent.policy.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Consent.policy.modifierExtension</t>
@@ -838,10 +1026,6 @@
     <t>Consent.verification.verified</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>Has been verified</t>
   </si>
   <si>
@@ -990,10 +1174,6 @@
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Security Labels that define affected resources</t>
@@ -1434,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
@@ -1465,7 +1645,7 @@
     <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1474,7 +1654,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.85546875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="46.53125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2902,28 +3082,28 @@
         <v>77</v>
       </c>
       <c r="S13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="T13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X13" t="s" s="2">
+      <c r="Y13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2970,10 +3150,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2981,11 +3161,11 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G14" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
@@ -2993,10 +3173,10 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>175</v>
@@ -3014,89 +3194,89 @@
         <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3105,19 +3285,19 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3155,16 +3335,16 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>184</v>
@@ -3173,33 +3353,33 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3210,7 +3390,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3222,18 +3402,20 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3281,13 +3463,13 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
@@ -3296,35 +3478,35 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3333,20 +3515,18 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3395,43 +3575,43 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3447,18 +3627,20 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3495,19 +3677,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3519,27 +3701,27 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3562,18 +3744,20 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3582,7 +3766,7 @@
         <v>77</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>77</v>
@@ -3621,7 +3805,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3639,10 +3823,10 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3650,10 +3834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3664,7 +3848,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3673,18 +3857,20 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3733,13 +3919,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3751,10 +3937,10 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3762,10 +3948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3785,19 +3971,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3806,7 +3994,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -3845,7 +4033,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3857,16 +4045,16 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3874,21 +4062,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3897,21 +4085,21 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -3959,28 +4147,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -3988,45 +4176,45 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4075,28 +4263,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4104,10 +4292,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4127,19 +4315,23 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4187,7 +4379,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4196,7 +4388,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4205,10 +4397,10 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4227,10 +4419,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4239,20 +4431,18 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>246</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4262,7 +4452,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4277,13 +4467,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4304,36 +4494,36 @@
         <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4341,7 +4531,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4356,20 +4546,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4393,13 +4581,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4417,7 +4605,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4426,30 +4614,30 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4460,7 +4648,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4472,15 +4660,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4529,13 +4719,13 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
@@ -4544,35 +4734,35 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4581,18 +4771,20 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4641,43 +4833,43 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4693,20 +4885,18 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4755,7 +4945,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4767,63 +4957,61 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4871,28 +5059,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4900,10 +5088,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4914,7 +5102,7 @@
         <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -4923,16 +5111,16 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4983,13 +5171,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -5012,10 +5200,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5038,13 +5226,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5095,7 +5283,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5107,7 +5295,7 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
@@ -5116,7 +5304,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5124,21 +5312,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5150,15 +5338,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5207,19 +5397,19 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5228,7 +5418,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5236,42 +5426,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5319,19 +5513,19 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -5340,7 +5534,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5348,10 +5542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5359,7 +5553,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5374,13 +5568,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5431,7 +5625,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5440,10 +5634,10 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5452,7 +5646,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5460,21 +5654,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5486,16 +5680,16 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>137</v>
+        <v>309</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5545,19 +5739,19 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5566,7 +5760,7 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5574,45 +5768,45 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>238</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>143</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5637,13 +5831,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5661,19 +5855,19 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -5682,7 +5876,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5690,10 +5884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5701,10 +5895,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5716,13 +5910,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5749,13 +5943,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5773,13 +5967,13 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
@@ -5802,10 +5996,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5825,16 +6019,16 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>283</v>
+        <v>174</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>285</v>
+        <v>176</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5885,7 +6079,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5897,7 +6091,7 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5906,7 +6100,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5914,14 +6108,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5940,22 +6134,22 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>287</v>
+        <v>135</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>77</v>
       </c>
@@ -5999,7 +6193,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6011,7 +6205,7 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6020,7 +6214,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6028,42 +6222,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6111,19 +6309,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>230</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6132,7 +6330,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6140,21 +6338,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6163,20 +6361,18 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>135</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6225,19 +6421,19 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6246,7 +6442,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6254,46 +6450,42 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>327</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6341,19 +6533,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6362,7 +6554,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6370,10 +6562,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6381,7 +6573,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6396,13 +6588,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6429,13 +6621,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>296</v>
+        <v>77</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6453,10 +6645,10 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>88</v>
@@ -6482,10 +6674,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6505,16 +6697,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6565,10 +6757,10 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>88</v>
@@ -6594,10 +6786,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6608,7 +6800,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6617,27 +6809,23 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>303</v>
+        <v>175</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q46" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
         <v>77</v>
       </c>
@@ -6657,13 +6845,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -6681,19 +6869,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>302</v>
+        <v>177</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6702,7 +6890,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6710,14 +6898,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6733,19 +6921,19 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>311</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>312</v>
+        <v>135</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>313</v>
+        <v>180</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>314</v>
+        <v>137</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6771,13 +6959,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6795,7 +6983,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6807,7 +6995,7 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -6816,7 +7004,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6824,14 +7012,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6844,24 +7032,26 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>311</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6885,13 +7075,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6909,7 +7099,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6921,7 +7111,7 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -6930,7 +7120,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -6938,10 +7128,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6949,10 +7139,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -6964,17 +7154,15 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>311</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -6999,13 +7187,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7023,13 +7211,13 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7052,10 +7240,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7066,7 +7254,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7078,17 +7266,15 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>167</v>
+        <v>345</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7113,13 +7299,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7137,13 +7323,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7166,10 +7352,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7180,7 +7366,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7189,25 +7375,25 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="R51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7251,13 +7437,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -7280,10 +7466,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7294,7 +7480,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7303,25 +7489,23 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>176</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q52" t="s" s="2">
-        <v>342</v>
-      </c>
+      <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7365,19 +7549,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7386,7 +7570,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7394,21 +7578,21 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7420,15 +7604,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7477,19 +7663,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7498,7 +7684,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7506,14 +7692,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>133</v>
+        <v>299</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7526,24 +7712,26 @@
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7591,7 +7779,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7612,7 +7800,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7620,46 +7808,42 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>237</v>
+        <v>356</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7683,13 +7867,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7707,19 +7891,19 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>239</v>
+        <v>355</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -7728,7 +7912,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7736,10 +7920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7759,16 +7943,16 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>108</v>
+        <v>361</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7795,13 +7979,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>349</v>
+        <v>77</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -7819,7 +8003,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>88</v>
@@ -7848,10 +8032,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7859,10 +8043,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -7874,20 +8058,24 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>352</v>
+        <v>167</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="R57" t="s" s="2">
         <v>77</v>
       </c>
@@ -7907,13 +8095,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -7931,13 +8119,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -7960,10 +8148,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7983,18 +8171,20 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8019,13 +8209,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>77</v>
+        <v>377</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8043,7 +8233,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8067,6 +8257,1254 @@
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -779,14 +779,6 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="59284-0"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
@@ -803,6 +795,45 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Consent.category.id</t>
+  </si>
+  <si>
+    <t>Consent.category.extension</t>
+  </si>
+  <si>
+    <t>Consent.category.coding</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.code</t>
+  </si>
+  <si>
+    <t>59284-0</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.category.text</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -1003,6 +1034,48 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.id</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.code</t>
+  </si>
+  <si>
+    <t>699237001</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.policyRule.text</t>
+  </si>
+  <si>
+    <t>Consent policy</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -1614,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
@@ -4452,7 +4525,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -4470,10 +4543,10 @@
         <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4506,24 +4579,24 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4531,7 +4604,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4543,20 +4616,18 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4605,7 +4676,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4617,38 +4688,38 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4657,19 +4728,19 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4707,55 +4778,55 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4774,18 +4845,20 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>187</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>188</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4833,7 +4906,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>191</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4848,35 +4921,35 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4885,16 +4958,16 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>176</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4945,50 +5018,50 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4997,19 +5070,19 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
+        <v>137</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5047,40 +5120,40 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5088,10 +5161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5099,10 +5172,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5111,19 +5184,23 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5132,7 +5209,7 @@
         <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>77</v>
@@ -5171,13 +5248,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>202</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -5189,10 +5266,10 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5200,10 +5277,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5223,18 +5300,20 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5283,7 +5362,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5295,16 +5374,16 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5312,21 +5391,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5335,21 +5414,21 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5358,7 +5437,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5397,28 +5476,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5426,45 +5505,43 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5513,28 +5590,28 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5542,10 +5619,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5553,7 +5630,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5565,19 +5642,23 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5625,7 +5706,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5634,7 +5715,7 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
@@ -5643,10 +5724,10 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5654,10 +5735,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5677,21 +5758,23 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>237</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5739,7 +5822,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>241</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5748,7 +5831,7 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -5757,10 +5840,10 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5768,10 +5851,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5779,7 +5862,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -5794,20 +5877,18 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>269</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5831,13 +5912,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5855,7 +5936,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5864,30 +5945,30 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5898,7 +5979,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5910,15 +5991,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5967,13 +6050,13 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
@@ -5982,35 +6065,35 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6019,18 +6102,20 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>175</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6079,43 +6164,43 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>133</v>
+        <v>293</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6131,20 +6216,18 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>294</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6193,7 +6276,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>184</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6205,50 +6288,50 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>299</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>300</v>
@@ -6257,11 +6340,9 @@
         <v>301</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6309,28 +6390,28 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6338,10 +6419,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6349,10 +6430,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6361,16 +6442,16 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>228</v>
+        <v>305</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6421,13 +6502,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6450,10 +6531,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6476,13 +6557,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>327</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>175</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>176</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6533,7 +6614,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6545,7 +6626,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6554,7 +6635,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6562,21 +6643,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6588,15 +6669,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>135</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6645,19 +6728,19 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6666,7 +6749,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6674,42 +6757,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6757,19 +6844,19 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6778,7 +6865,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6786,10 +6873,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6812,13 +6899,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>176</v>
+        <v>317</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6869,7 +6956,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6878,10 +6965,10 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6890,7 +6977,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6898,21 +6985,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6924,16 +7011,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>180</v>
+        <v>307</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6983,19 +7070,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>184</v>
+        <v>319</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7004,7 +7091,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7012,45 +7099,45 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>143</v>
+        <v>326</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7075,13 +7162,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7099,19 +7186,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7120,7 +7207,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7128,10 +7215,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7139,7 +7226,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>88</v>
@@ -7151,16 +7238,16 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
+        <v>176</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7187,13 +7274,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7211,7 +7298,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>177</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7223,7 +7310,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7232,7 +7319,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7240,21 +7327,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7263,18 +7350,20 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7311,31 +7400,31 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>344</v>
+        <v>184</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7344,7 +7433,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7352,10 +7441,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7375,25 +7464,27 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>293</v>
+        <v>186</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>349</v>
+        <v>187</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7437,7 +7528,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>191</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7455,10 +7546,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7466,10 +7557,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7578,10 +7669,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7651,16 +7742,16 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>184</v>
@@ -7692,45 +7783,45 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>300</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>301</v>
+        <v>198</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7740,7 +7831,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -7779,28 +7870,28 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>302</v>
+        <v>202</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7808,10 +7899,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7819,7 +7910,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -7831,18 +7922,20 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>206</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7867,13 +7960,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7891,10 +7984,10 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>88</v>
@@ -7909,10 +8002,10 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7920,10 +8013,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7931,7 +8024,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>88</v>
@@ -7943,19 +8036,21 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>361</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>362</v>
+        <v>213</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>363</v>
+        <v>214</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -7964,7 +8059,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8003,10 +8098,10 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>217</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>88</v>
@@ -8021,10 +8116,10 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8032,10 +8127,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8046,7 +8141,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8058,24 +8153,22 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>368</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8095,13 +8188,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8119,13 +8212,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>224</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8137,10 +8230,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8148,10 +8241,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8162,7 +8255,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8174,18 +8267,20 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>229</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>230</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8209,13 +8304,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8233,13 +8328,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>233</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8251,10 +8346,10 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8262,10 +8357,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8276,7 +8371,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8288,18 +8383,20 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>237</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>238</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8308,7 +8405,7 @@
         <v>77</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>77</v>
@@ -8323,13 +8420,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>382</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8347,13 +8444,13 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>241</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -8365,10 +8462,10 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8376,10 +8473,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8402,17 +8499,15 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>186</v>
+        <v>305</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8437,13 +8532,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8461,7 +8556,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8490,10 +8585,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8504,7 +8599,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8513,20 +8608,18 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>391</v>
+        <v>175</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8551,13 +8644,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8575,19 +8668,19 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>390</v>
+        <v>177</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
@@ -8596,7 +8689,7 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8604,21 +8697,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8627,19 +8720,19 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>345</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>397</v>
+        <v>135</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>398</v>
+        <v>180</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>399</v>
+        <v>137</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8689,19 +8782,19 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>396</v>
+        <v>184</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8710,7 +8803,7 @@
         <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8718,14 +8811,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>400</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8738,28 +8831,30 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>403</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8803,7 +8898,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>400</v>
+        <v>314</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8815,7 +8910,7 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8824,7 +8919,7 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8832,10 +8927,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8843,7 +8938,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
@@ -8855,16 +8950,16 @@
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>176</v>
+        <v>351</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8915,10 +9010,10 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>88</v>
@@ -8927,7 +9022,7 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -8936,7 +9031,7 @@
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8944,21 +9039,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>352</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>405</v>
+        <v>352</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -8970,17 +9065,15 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9029,19 +9122,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>184</v>
+        <v>352</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9050,7 +9143,7 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9058,46 +9151,42 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>406</v>
+        <v>356</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>356</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>299</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9145,19 +9234,19 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9166,7 +9255,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9174,10 +9263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9200,13 +9289,13 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>108</v>
+        <v>305</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>409</v>
+        <v>361</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9233,13 +9322,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>410</v>
+        <v>77</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>411</v>
+        <v>77</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9257,10 +9346,10 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>88</v>
@@ -9286,10 +9375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9297,7 +9386,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9309,16 +9398,16 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>413</v>
+        <v>174</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>414</v>
+        <v>175</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>415</v>
+        <v>176</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9369,10 +9458,10 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>412</v>
+        <v>177</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>88</v>
@@ -9381,7 +9470,7 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9390,7 +9479,7 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9398,14 +9487,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>416</v>
+        <v>363</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>416</v>
+        <v>363</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9424,15 +9513,17 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>417</v>
+        <v>135</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9481,7 +9572,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>416</v>
+        <v>184</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9493,18 +9584,2516 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AK71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1030,10 +1030,7 @@
     <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
   </si>
   <si>
-    <t>Regulatory policy examples.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-patient-consent-for-sms-notifications</t>
   </si>
   <si>
     <t>Consent.policyRule.id</t>
@@ -1043,33 +1040,6 @@
   </si>
   <si>
     <t>Consent.policyRule.coding</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.code</t>
-  </si>
-  <si>
-    <t>699237001</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.policyRule.coding.userSelected</t>
   </si>
   <si>
     <t>Consent.policyRule.text</t>
@@ -1687,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
@@ -1715,7 +1685,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.23828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -7110,7 +7080,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
@@ -7162,13 +7132,11 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y48" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y48" s="2"/>
+      <c r="Z48" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7215,10 +7183,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7327,10 +7295,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7441,10 +7409,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7557,10 +7525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7580,19 +7548,23 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7601,7 +7573,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7640,7 +7612,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7652,16 +7624,16 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7676,7 +7648,7 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7692,20 +7664,18 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>134</v>
+        <v>305</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7742,19 +7712,19 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7766,7 +7736,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7775,7 +7745,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7783,10 +7753,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7806,23 +7776,19 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7831,7 +7797,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -7870,7 +7836,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7882,16 +7848,16 @@
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7899,21 +7865,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7922,19 +7888,19 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>208</v>
+        <v>137</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7984,28 +7950,28 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8013,43 +7979,45 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>213</v>
+        <v>312</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8059,7 +8027,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8098,28 +8066,28 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>217</v>
+        <v>314</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8138,7 +8106,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>88</v>
@@ -8153,18 +8121,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>221</v>
+        <v>340</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>222</v>
+        <v>341</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8212,10 +8178,10 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>224</v>
+        <v>339</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>88</v>
@@ -8230,10 +8196,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8241,10 +8207,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8264,23 +8230,19 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>228</v>
+        <v>343</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>229</v>
+        <v>344</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8328,7 +8290,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8346,10 +8308,10 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8357,10 +8319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8380,23 +8342,19 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>237</v>
+        <v>347</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8405,7 +8363,7 @@
         <v>77</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>77</v>
@@ -8444,7 +8402,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8462,10 +8420,10 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8473,10 +8431,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8484,10 +8442,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8502,10 +8460,10 @@
         <v>305</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8556,13 +8514,13 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
@@ -8585,10 +8543,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8697,10 +8655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8811,10 +8769,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8927,10 +8885,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8953,13 +8911,13 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8986,13 +8944,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9010,10 +8968,10 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>88</v>
@@ -9039,10 +8997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9062,16 +9020,16 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9122,7 +9080,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9151,10 +9109,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9165,7 +9123,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9177,20 +9135,22 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="R66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9234,13 +9194,13 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
@@ -9263,10 +9223,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9274,7 +9234,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -9286,16 +9246,16 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>305</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>360</v>
+        <v>175</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>361</v>
+        <v>176</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9346,7 +9306,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>359</v>
+        <v>177</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9358,7 +9318,7 @@
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
@@ -9367,7 +9327,7 @@
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9375,21 +9335,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9401,15 +9361,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9458,19 +9420,19 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9487,14 +9449,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>133</v>
+        <v>311</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9507,24 +9469,26 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9572,7 +9536,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>184</v>
+        <v>314</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9593,7 +9557,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9601,46 +9565,42 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9664,13 +9624,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9688,19 +9648,19 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>314</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9709,7 +9669,7 @@
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9717,10 +9677,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9740,16 +9700,16 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>108</v>
+        <v>377</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9776,13 +9736,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -9800,10 +9760,10 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>88</v>
@@ -9829,10 +9789,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9843,7 +9803,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -9855,20 +9815,24 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>371</v>
+        <v>167</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="R72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9888,13 +9852,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -9912,13 +9876,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
@@ -9941,10 +9905,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9964,25 +9928,25 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>305</v>
+        <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q73" t="s" s="2">
-        <v>377</v>
-      </c>
+      <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10002,13 +9966,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10026,7 +9990,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10055,10 +10019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10069,7 +10033,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10078,18 +10042,20 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>175</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10114,13 +10080,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10138,19 +10104,19 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>177</v>
+        <v>394</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10159,7 +10125,7 @@
         <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10167,14 +10133,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10190,19 +10156,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>180</v>
+        <v>402</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>137</v>
+        <v>403</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10228,13 +10194,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>404</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10252,7 +10218,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>184</v>
+        <v>400</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10264,7 +10230,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10273,7 +10239,7 @@
         <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10281,14 +10247,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10301,26 +10267,24 @@
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>312</v>
+        <v>407</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>313</v>
+        <v>408</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10344,13 +10308,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>77</v>
+        <v>411</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10368,7 +10332,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>314</v>
+        <v>406</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10380,7 +10344,7 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
@@ -10389,7 +10353,7 @@
         <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -10397,10 +10361,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10408,7 +10372,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>88</v>
@@ -10420,18 +10384,20 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>167</v>
+        <v>361</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10456,13 +10422,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -10480,10 +10446,10 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>88</v>
@@ -10509,10 +10475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10520,10 +10486,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10532,23 +10498,25 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>387</v>
+        <v>305</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="R78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10592,13 +10560,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -10613,7 +10581,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10621,10 +10589,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10635,7 +10603,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10644,27 +10612,23 @@
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>391</v>
+        <v>175</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q79" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10684,13 +10648,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -10708,19 +10672,19 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>390</v>
+        <v>177</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
@@ -10729,7 +10693,7 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10737,14 +10701,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10760,19 +10724,19 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>399</v>
+        <v>135</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>401</v>
+        <v>137</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10798,13 +10762,13 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -10822,7 +10786,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>398</v>
+        <v>184</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10834,7 +10798,7 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -10843,7 +10807,7 @@
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -10851,14 +10815,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10871,24 +10835,26 @@
         <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>406</v>
+        <v>313</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -10912,13 +10878,13 @@
         <v>77</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>408</v>
+        <v>77</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>77</v>
@@ -10936,7 +10902,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>404</v>
+        <v>314</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10948,7 +10914,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10957,7 +10923,7 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -10965,10 +10931,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10976,10 +10942,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -10991,17 +10957,15 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11026,13 +10990,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11050,13 +11014,13 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
@@ -11079,10 +11043,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11090,10 +11054,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
@@ -11105,17 +11069,15 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>167</v>
+        <v>429</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -11140,13 +11102,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>421</v>
+        <v>77</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -11164,13 +11126,13 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
@@ -11193,10 +11155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11207,7 +11169,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -11216,20 +11178,18 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11278,13 +11238,13 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
@@ -11302,798 +11262,6 @@
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q85" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="R85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN91" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -277,6 +277,9 @@
     <t>FinancialConsent</t>
   </si>
   <si>
+    <t>infrastructure.information</t>
+  </si>
+  <si>
     <t>Consent.id</t>
   </si>
   <si>
@@ -360,7 +363,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -418,6 +421,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -458,7 +465,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -480,12 +487,6 @@
     <t>This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
   </si>
   <si>
-    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="urn:ietf:rfc:3986"/&gt;
-  &lt;value value="Local eCMS identifier"/&gt;
-&lt;/valueIdentifier&gt;</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -516,7 +517,7 @@
     <t>Indicates the state of the consent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -556,105 +557,105 @@
     <t>Consent.scope.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.scope.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/consentscope</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Consent.scope.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Consent.scope.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/consentscope</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Consent.scope.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -970,6 +971,10 @@
     <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
     <t>Consent.policy.id</t>
   </si>
   <si>
@@ -1127,7 +1132,7 @@
     <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.3.0</t>
   </si>
   <si>
     <t>Consent.provision.period</t>
@@ -1333,7 +1338,7 @@
     <t>How a resource reference is interpreted when testing consent restrictions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.3.0</t>
   </si>
   <si>
     <t>Consent.provision.data.reference</t>
@@ -1679,7 +1684,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="42.44921875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1934,15 +1939,15 @@
         <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1953,7 +1958,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1962,19 +1967,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2024,13 +2029,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2067,7 +2072,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2076,16 +2081,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2136,19 +2141,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2165,10 +2170,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2179,28 +2184,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2250,19 +2255,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2279,10 +2284,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2293,7 +2298,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2305,16 +2310,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2340,13 +2345,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2364,19 +2369,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2393,21 +2398,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2419,16 +2424,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2478,19 +2483,19 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2499,7 +2504,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2507,14 +2512,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2533,16 +2538,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2592,7 +2597,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2604,7 +2609,7 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
@@ -2613,7 +2618,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2621,14 +2626,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2647,16 +2652,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2706,7 +2711,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2718,7 +2723,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2727,7 +2732,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2735,14 +2740,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2755,25 +2760,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2822,7 +2827,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2834,7 +2839,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2843,7 +2848,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2851,10 +2856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2874,19 +2879,19 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2900,7 +2905,7 @@
         <v>77</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>77</v>
@@ -2936,7 +2941,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2948,27 +2953,27 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2976,34 +2981,34 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3028,13 +3033,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3052,39 +3057,39 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3092,28 +3097,28 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3140,13 +3145,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3164,19 +3169,19 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
@@ -3193,10 +3198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3207,7 +3212,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3219,7 +3224,7 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>175</v>
@@ -3282,7 +3287,7 @@
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
@@ -3312,7 +3317,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3331,16 +3336,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3402,7 +3407,7 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
@@ -3442,7 +3447,7 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -3518,7 +3523,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3549,7 +3554,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3561,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>175</v>
@@ -3624,7 +3629,7 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3654,7 +3659,7 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3673,16 +3678,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3744,7 +3749,7 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
@@ -3775,7 +3780,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3784,10 +3789,10 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>197</v>
@@ -3854,13 +3859,13 @@
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3891,7 +3896,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3900,19 +3905,19 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3962,28 +3967,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3991,10 +3996,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4005,7 +4010,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4014,20 +4019,20 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4037,7 +4042,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4076,28 +4081,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4105,10 +4110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4119,7 +4124,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4128,20 +4133,20 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4190,28 +4195,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4219,10 +4224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4233,7 +4238,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4242,22 +4247,22 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4306,28 +4311,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4335,10 +4340,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4349,7 +4354,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4358,22 +4363,22 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4422,28 +4427,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4451,10 +4456,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4462,7 +4467,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4474,16 +4479,16 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4510,13 +4515,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4534,10 +4539,10 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -4546,27 +4551,27 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4577,7 +4582,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4589,7 +4594,7 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>175</v>
@@ -4652,7 +4657,7 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4675,14 +4680,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4701,16 +4706,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4772,7 +4777,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4789,10 +4794,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4812,7 +4817,7 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>186</v>
@@ -4888,7 +4893,7 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
@@ -4905,10 +4910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4919,7 +4924,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4931,7 +4936,7 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>175</v>
@@ -4994,7 +4999,7 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5017,14 +5022,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5043,16 +5048,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5114,7 +5119,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5131,10 +5136,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5145,7 +5150,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5154,10 +5159,10 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>197</v>
@@ -5179,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>77</v>
@@ -5224,13 +5229,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -5247,10 +5252,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5261,7 +5266,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5270,19 +5275,19 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5332,28 +5337,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5361,10 +5366,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5375,7 +5380,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5384,20 +5389,20 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5407,7 +5412,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5446,28 +5451,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5475,10 +5480,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,7 +5494,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5498,20 +5503,20 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5560,28 +5565,28 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5589,10 +5594,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5603,7 +5608,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5612,22 +5617,22 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5676,28 +5681,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5705,10 +5710,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5719,7 +5724,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5728,22 +5733,22 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5792,28 +5797,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5821,10 +5826,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5832,10 +5837,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5844,19 +5849,19 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5906,39 +5911,39 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5949,7 +5954,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5958,19 +5963,19 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6020,43 +6025,43 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6072,19 +6077,19 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6134,7 +6139,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6146,31 +6151,31 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6186,16 +6191,16 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6246,7 +6251,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6258,10 +6263,10 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -6270,15 +6275,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6289,7 +6294,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6298,19 +6303,19 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6360,25 +6365,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6389,10 +6394,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6415,13 +6420,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6472,7 +6477,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6484,7 +6489,7 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6501,10 +6506,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6515,7 +6520,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6527,7 +6532,7 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>175</v>
@@ -6590,7 +6595,7 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6613,14 +6618,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6639,16 +6644,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M44" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6710,7 +6715,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6727,14 +6732,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6747,25 +6752,25 @@
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6814,7 +6819,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6826,7 +6831,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6835,7 +6840,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6843,10 +6848,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,7 +6862,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6869,13 +6874,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6926,19 +6931,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6955,10 +6960,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6969,7 +6974,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6981,16 +6986,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7040,19 +7045,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7069,10 +7074,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7080,10 +7085,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7092,22 +7097,22 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7132,11 +7137,11 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7154,19 +7159,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7183,10 +7188,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7197,7 +7202,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7209,7 +7214,7 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>175</v>
@@ -7272,7 +7277,7 @@
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7295,14 +7300,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7321,16 +7326,16 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7392,7 +7397,7 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7409,10 +7414,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7432,7 +7437,7 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>186</v>
@@ -7508,7 +7513,7 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
@@ -7525,10 +7530,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7539,7 +7544,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7548,22 +7553,22 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7573,7 +7578,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7612,28 +7617,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7641,10 +7646,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7664,16 +7669,16 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7724,7 +7729,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7736,7 +7741,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7753,10 +7758,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7767,7 +7772,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7779,7 +7784,7 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>175</v>
@@ -7842,7 +7847,7 @@
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7865,14 +7870,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7891,16 +7896,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7962,7 +7967,7 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -7979,14 +7984,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7999,25 +8004,25 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8066,7 +8071,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8078,7 +8083,7 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8087,7 +8092,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8095,10 +8100,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8106,10 +8111,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8118,16 +8123,16 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8178,19 +8183,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8207,10 +8212,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8221,7 +8226,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8233,13 +8238,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8290,19 +8295,19 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -8319,10 +8324,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8333,7 +8338,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8345,13 +8350,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8402,19 +8407,19 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8431,10 +8436,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8442,10 +8447,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8454,16 +8459,16 @@
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8514,19 +8519,19 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8543,10 +8548,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8557,7 +8562,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8569,7 +8574,7 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>175</v>
@@ -8632,7 +8637,7 @@
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8655,14 +8660,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8681,16 +8686,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8752,7 +8757,7 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8769,14 +8774,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8789,25 +8794,25 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8856,7 +8861,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8868,7 +8873,7 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8877,7 +8882,7 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8885,10 +8890,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8896,10 +8901,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -8908,16 +8913,16 @@
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8944,13 +8949,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -8968,19 +8973,19 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -8997,10 +9002,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9011,7 +9016,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9020,16 +9025,16 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9080,19 +9085,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9109,10 +9114,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9135,13 +9140,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9149,7 +9154,7 @@
         <v>77</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>77</v>
@@ -9194,7 +9199,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9206,7 +9211,7 @@
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9223,10 +9228,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9237,7 +9242,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9249,7 +9254,7 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>175</v>
@@ -9312,7 +9317,7 @@
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -9335,14 +9340,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9361,16 +9366,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9432,7 +9437,7 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9449,14 +9454,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9469,25 +9474,25 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9536,7 +9541,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9548,7 +9553,7 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
@@ -9557,7 +9562,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9565,10 +9570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9576,10 +9581,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9591,13 +9596,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9624,13 +9629,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9648,19 +9653,19 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9677,10 +9682,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9688,10 +9693,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9703,13 +9708,13 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9760,19 +9765,19 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9789,10 +9794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9812,26 +9817,26 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q72" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="R72" t="s" s="2">
         <v>77</v>
@@ -9852,13 +9857,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -9876,7 +9881,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9888,7 +9893,7 @@
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -9905,10 +9910,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9928,19 +9933,19 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9966,13 +9971,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9990,7 +9995,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10002,7 +10007,7 @@
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
@@ -10019,10 +10024,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10042,19 +10047,19 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10080,13 +10085,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10104,7 +10109,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10116,7 +10121,7 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10133,10 +10138,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10156,19 +10161,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10194,13 +10199,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10218,7 +10223,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10230,7 +10235,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10247,10 +10252,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10270,19 +10275,19 @@
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10308,13 +10313,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10332,7 +10337,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10344,7 +10349,7 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
@@ -10361,10 +10366,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10375,7 +10380,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
@@ -10384,19 +10389,19 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10446,19 +10451,19 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -10475,10 +10480,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10498,16 +10503,16 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10515,7 +10520,7 @@
         <v>77</v>
       </c>
       <c r="Q78" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="R78" t="s" s="2">
         <v>77</v>
@@ -10560,7 +10565,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10572,7 +10577,7 @@
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -10581,7 +10586,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10589,10 +10594,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10603,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10615,7 +10620,7 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>175</v>
@@ -10678,7 +10683,7 @@
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
@@ -10701,14 +10706,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10727,16 +10732,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10798,7 +10803,7 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -10815,14 +10820,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10835,25 +10840,25 @@
         <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10902,7 +10907,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10914,7 +10919,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10923,7 +10928,7 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -10931,10 +10936,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10942,10 +10947,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -10954,16 +10959,16 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10990,13 +10995,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11014,19 +11019,19 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
@@ -11043,10 +11048,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11054,10 +11059,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
@@ -11066,16 +11071,16 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11126,19 +11131,19 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
@@ -11155,10 +11160,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11184,10 +11189,10 @@
         <v>80</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11238,7 +11243,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11250,7 +11255,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -277,9 +277,6 @@
     <t>FinancialConsent</t>
   </si>
   <si>
-    <t>infrastructure.information</t>
-  </si>
-  <si>
     <t>Consent.id</t>
   </si>
   <si>
@@ -363,7 +360,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -421,10 +418,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -465,7 +458,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -487,6 +480,12 @@
     <t>This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
   </si>
   <si>
+    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="urn:ietf:rfc:3986"/&gt;
+  &lt;value value="Local eCMS identifier"/&gt;
+&lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -517,7 +516,7 @@
     <t>Indicates the state of the consent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -557,6 +556,10 @@
     <t>Consent.scope.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -652,10 +655,6 @@
     <t>Consent.scope.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -971,10 +970,6 @@
     <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
     <t>Consent.policy.id</t>
   </si>
   <si>
@@ -1132,7 +1127,7 @@
     <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.period</t>
@@ -1338,7 +1333,7 @@
     <t>How a resource reference is interpreted when testing consent restrictions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.data.reference</t>
@@ -1684,7 +1679,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="42.44921875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1939,15 +1934,15 @@
         <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1958,28 +1953,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2029,13 +2024,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2072,25 +2067,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2141,19 +2136,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2170,10 +2165,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2184,28 +2179,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2255,19 +2250,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2284,10 +2279,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2298,7 +2293,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2310,16 +2305,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2345,43 +2340,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2398,21 +2393,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2424,16 +2419,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2483,28 +2478,28 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2512,14 +2507,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2538,16 +2533,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2597,7 +2592,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2609,7 +2604,7 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
@@ -2618,7 +2613,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2626,14 +2621,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2652,16 +2647,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2711,7 +2706,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2723,7 +2718,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2732,7 +2727,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2740,14 +2735,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2760,25 +2755,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2827,7 +2822,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2839,7 +2834,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2848,7 +2843,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2856,10 +2851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2879,19 +2874,19 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2905,7 +2900,7 @@
         <v>77</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="U11" t="s" s="2">
         <v>77</v>
@@ -2941,7 +2936,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2953,27 +2948,27 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2981,34 +2976,34 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G12" t="s" s="2">
+      <c r="J12" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3033,63 +3028,63 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3097,28 +3092,28 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G13" t="s" s="2">
+      <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3145,14 +3140,14 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3169,19 +3164,19 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3212,7 +3207,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3224,7 +3219,7 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>175</v>
@@ -3287,7 +3282,7 @@
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
@@ -3317,7 +3312,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3336,16 +3331,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3407,7 +3402,7 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
@@ -3447,7 +3442,7 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>186</v>
@@ -3523,7 +3518,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3554,7 +3549,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3566,7 +3561,7 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>175</v>
@@ -3629,7 +3624,7 @@
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3659,7 +3654,7 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3678,16 +3673,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3749,7 +3744,7 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
@@ -3780,19 +3775,19 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>197</v>
@@ -3859,13 +3854,13 @@
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3896,28 +3891,28 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3967,28 +3962,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3996,10 +3991,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4010,29 +4005,29 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4042,67 +4037,67 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="T21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF21" t="s" s="2">
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4110,10 +4105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4124,29 +4119,29 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4195,28 +4190,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4224,10 +4219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4238,31 +4233,31 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4311,28 +4306,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4340,10 +4335,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4354,31 +4349,31 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4427,28 +4422,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4456,10 +4451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4467,7 +4462,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4479,16 +4474,16 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4515,14 +4510,14 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4539,10 +4534,10 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -4551,27 +4546,27 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4582,7 +4577,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4594,7 +4589,7 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>175</v>
@@ -4657,7 +4652,7 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4680,14 +4675,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4706,16 +4701,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4777,7 +4772,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4794,10 +4789,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4817,7 +4812,7 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>186</v>
@@ -4893,7 +4888,7 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
@@ -4910,10 +4905,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4924,7 +4919,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4936,7 +4931,7 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>175</v>
@@ -4999,7 +4994,7 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -5022,14 +5017,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5048,16 +5043,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5119,7 +5114,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5136,10 +5131,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5150,19 +5145,19 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>197</v>
@@ -5184,7 +5179,7 @@
         <v>77</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>77</v>
@@ -5229,13 +5224,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -5252,10 +5247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5266,28 +5261,28 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5337,28 +5332,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5366,10 +5361,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5380,29 +5375,29 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5412,7 +5407,7 @@
         <v>77</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>77</v>
@@ -5451,28 +5446,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5480,10 +5475,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5494,29 +5489,29 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5565,28 +5560,28 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5594,10 +5589,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5608,31 +5603,31 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K35" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5681,28 +5676,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5710,10 +5705,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5724,31 +5719,31 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5797,28 +5792,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5826,10 +5821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5837,31 +5832,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5911,39 +5906,39 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5954,28 +5949,28 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6025,43 +6020,43 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6077,19 +6072,19 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6139,7 +6134,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6151,31 +6146,31 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6191,16 +6186,16 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6251,7 +6246,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6263,10 +6258,10 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -6275,15 +6270,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6294,28 +6289,28 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6365,25 +6360,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6394,10 +6389,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6420,13 +6415,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6477,7 +6472,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6489,7 +6484,7 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6506,10 +6501,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6520,7 +6515,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6532,7 +6527,7 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>175</v>
@@ -6595,7 +6590,7 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6618,14 +6613,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6644,16 +6639,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M44" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6715,7 +6710,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6732,14 +6727,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6752,25 +6747,25 @@
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6819,7 +6814,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6831,7 +6826,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6840,7 +6835,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6848,10 +6843,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6862,7 +6857,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6874,13 +6869,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6931,19 +6926,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6960,10 +6955,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6974,7 +6969,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6986,16 +6981,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7045,19 +7040,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7074,10 +7069,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7085,34 +7080,34 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G48" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7137,11 +7132,11 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -7159,19 +7154,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7188,10 +7183,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7202,7 +7197,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7209,7 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>175</v>
@@ -7277,7 +7272,7 @@
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
@@ -7300,14 +7295,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7326,16 +7321,16 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7397,7 +7392,7 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7414,10 +7409,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7437,7 +7432,7 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>186</v>
@@ -7513,7 +7508,7 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
@@ -7530,10 +7525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7544,31 +7539,31 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7578,7 +7573,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7617,28 +7612,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7646,10 +7641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7669,16 +7664,16 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7729,7 +7724,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7741,7 +7736,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7758,10 +7753,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7772,7 +7767,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7784,7 +7779,7 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>175</v>
@@ -7847,7 +7842,7 @@
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7870,14 +7865,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7896,16 +7891,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7967,7 +7962,7 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -7984,14 +7979,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8004,25 +7999,25 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8071,7 +8066,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8083,7 +8078,7 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8092,7 +8087,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8100,10 +8095,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8111,28 +8106,28 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8183,19 +8178,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8212,10 +8207,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8226,7 +8221,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8238,13 +8233,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8295,19 +8290,19 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
@@ -8324,10 +8319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8338,7 +8333,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8350,13 +8345,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8407,19 +8402,19 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8436,10 +8431,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8447,28 +8442,28 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8519,19 +8514,19 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8548,10 +8543,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8562,7 +8557,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8574,7 +8569,7 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>175</v>
@@ -8637,7 +8632,7 @@
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8660,14 +8655,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8686,16 +8681,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8757,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
@@ -8774,14 +8769,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8794,25 +8789,25 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8861,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8873,7 +8868,7 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8882,7 +8877,7 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8890,10 +8885,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8901,28 +8896,28 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8949,13 +8944,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -8973,19 +8968,19 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
@@ -9002,10 +8997,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9016,25 +9011,25 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K65" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9085,19 +9080,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -9114,10 +9109,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9140,13 +9135,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9154,7 +9149,7 @@
         <v>77</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>77</v>
@@ -9199,7 +9194,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9211,7 +9206,7 @@
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
@@ -9228,10 +9223,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9242,7 +9237,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9254,7 +9249,7 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>175</v>
@@ -9317,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -9340,14 +9335,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9366,16 +9361,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9437,7 +9432,7 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9454,14 +9449,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9474,25 +9469,25 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9541,7 +9536,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9553,7 +9548,7 @@
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
@@ -9562,7 +9557,7 @@
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9570,10 +9565,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9581,10 +9576,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9596,13 +9591,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9629,13 +9624,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9653,19 +9648,19 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9682,10 +9677,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9693,10 +9688,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9708,13 +9703,13 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9765,19 +9760,19 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9794,10 +9789,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9817,54 +9812,54 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q72" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Y72" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="R72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X72" t="s" s="2">
+      <c r="Z72" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y72" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9881,7 +9876,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9893,7 +9888,7 @@
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -9910,10 +9905,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9933,19 +9928,19 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9971,13 +9966,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9995,7 +9990,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10007,7 +10002,7 @@
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
@@ -10024,10 +10019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10047,19 +10042,19 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10085,13 +10080,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10109,7 +10104,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10121,7 +10116,7 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
@@ -10138,10 +10133,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10161,19 +10156,19 @@
         <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10199,13 +10194,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10223,7 +10218,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10235,7 +10230,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10252,10 +10247,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10275,19 +10270,19 @@
         <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10313,13 +10308,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10337,7 +10332,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10349,7 +10344,7 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
@@ -10366,10 +10361,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10380,28 +10375,28 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10451,19 +10446,19 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -10480,10 +10475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10503,16 +10498,16 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10520,7 +10515,7 @@
         <v>77</v>
       </c>
       <c r="Q78" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R78" t="s" s="2">
         <v>77</v>
@@ -10565,7 +10560,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10577,7 +10572,7 @@
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -10586,7 +10581,7 @@
         <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10594,10 +10589,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10608,7 +10603,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10620,7 +10615,7 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>175</v>
@@ -10683,7 +10678,7 @@
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
@@ -10706,14 +10701,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10732,16 +10727,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>180</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10803,7 +10798,7 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
@@ -10820,14 +10815,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10840,25 +10835,25 @@
         <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10907,7 +10902,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10919,7 +10914,7 @@
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10928,7 +10923,7 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -10936,10 +10931,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10947,28 +10942,28 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K82" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10995,13 +10990,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11019,19 +11014,19 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
@@ -11048,10 +11043,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11059,28 +11054,28 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K83" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11131,19 +11126,19 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
@@ -11160,10 +11155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11189,10 +11184,10 @@
         <v>80</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11243,7 +11238,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11255,7 +11250,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
+++ b/branches/Richard/StructureDefinition-receive-sms-messages.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
